--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128714565</v>
+        <v>128715010</v>
       </c>
       <c r="B3" t="n">
-        <v>79708</v>
+        <v>79679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,14 +819,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Larstjärnen, Dlr</t>
+          <t>Smörtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380004</v>
+        <v>380156</v>
       </c>
       <c r="R3" t="n">
-        <v>6856113</v>
+        <v>6855940</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -858,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128715010</v>
+        <v>128714565</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>79708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Smörtjärnåsen, Dlr</t>
+          <t>Larstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380156</v>
+        <v>380004</v>
       </c>
       <c r="R4" t="n">
-        <v>6855940</v>
+        <v>6856113</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1340,40 +1340,36 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128715364</v>
+        <v>128713452</v>
       </c>
       <c r="B8" t="n">
-        <v>91431</v>
+        <v>79679</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1382,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380100</v>
+        <v>380159</v>
       </c>
       <c r="R8" t="n">
-        <v>6856114</v>
+        <v>6856070</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1674,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128713452</v>
+        <v>128713378</v>
       </c>
       <c r="B11" t="n">
-        <v>79679</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,26 +1681,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1712,13 +1717,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>380159</v>
+        <v>380085</v>
       </c>
       <c r="R11" t="n">
-        <v>6856070</v>
+        <v>6856048</v>
       </c>
       <c r="S11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,7 +1752,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,7 +1762,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128713378</v>
+        <v>128713160</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>79679</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,35 +1800,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1831,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380085</v>
+        <v>380089</v>
       </c>
       <c r="R12" t="n">
-        <v>6856048</v>
+        <v>6856030</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1866,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1876,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B13" t="n">
-        <v>79679</v>
+        <v>78492</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R13" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1976,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128712927</v>
+        <v>128713650</v>
       </c>
       <c r="B14" t="n">
-        <v>78492</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,25 +2020,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>380057</v>
+        <v>380134</v>
       </c>
       <c r="R14" t="n">
-        <v>6856033</v>
+        <v>6856126</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2096,7 +2096,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer på gammal tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,10 +2128,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128713650</v>
+        <v>128712913</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,29 +2139,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2165,13 +2166,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380134</v>
+        <v>380064</v>
       </c>
       <c r="R15" t="n">
-        <v>6856126</v>
+        <v>6856024</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,12 +2211,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer på gammal tall</t>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128712913</v>
+        <v>128713709</v>
       </c>
       <c r="B17" t="n">
-        <v>79708</v>
+        <v>78847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2403,13 +2404,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380064</v>
+        <v>380115</v>
       </c>
       <c r="R17" t="n">
-        <v>6856024</v>
+        <v>6856115</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2448,12 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,7 +2476,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128713709</v>
+        <v>128724114</v>
       </c>
       <c r="B18" t="n">
         <v>78847</v>
@@ -2509,22 +2505,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Larstjärnen, Dlr</t>
+          <t>Smörtjärnsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380115</v>
+        <v>380096</v>
       </c>
       <c r="R18" t="n">
-        <v>6856115</v>
+        <v>6855925</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2548,22 +2541,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,28 +2565,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128724114</v>
+        <v>128724111</v>
       </c>
       <c r="B19" t="n">
-        <v>78847</v>
+        <v>79679</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2625,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>380096</v>
+        <v>380091</v>
       </c>
       <c r="R19" t="n">
-        <v>6855925</v>
+        <v>6855928</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2660,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2670,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2698,48 +2692,55 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128724111</v>
+        <v>128715364</v>
       </c>
       <c r="B20" t="n">
-        <v>79679</v>
+        <v>91431</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Smörtjärnsåsen, Dlr</t>
+          <t>Larstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>380091</v>
+        <v>380100</v>
       </c>
       <c r="R20" t="n">
-        <v>6855928</v>
+        <v>6856114</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2763,22 +2764,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,19 +2788,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128713751</v>
+        <v>128714565</v>
       </c>
       <c r="B2" t="n">
-        <v>79679</v>
+        <v>79708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380101</v>
+        <v>380004</v>
       </c>
       <c r="R2" t="n">
-        <v>6856112</v>
+        <v>6856113</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128715010</v>
+        <v>128713751</v>
       </c>
       <c r="B3" t="n">
         <v>79679</v>
@@ -819,17 +819,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Smörtjärnåsen, Dlr</t>
+          <t>Larstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380156</v>
+        <v>380101</v>
       </c>
       <c r="R3" t="n">
-        <v>6855940</v>
+        <v>6856112</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128714565</v>
+        <v>128715010</v>
       </c>
       <c r="B4" t="n">
-        <v>79708</v>
+        <v>79679</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Larstjärnen, Dlr</t>
+          <t>Smörtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380004</v>
+        <v>380156</v>
       </c>
       <c r="R4" t="n">
-        <v>6856113</v>
+        <v>6855940</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128713452</v>
+        <v>128715329</v>
       </c>
       <c r="B8" t="n">
-        <v>79679</v>
+        <v>78061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380159</v>
+        <v>380141</v>
       </c>
       <c r="R8" t="n">
-        <v>6856070</v>
+        <v>6856087</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,7 +1450,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128713614</v>
+        <v>128713452</v>
       </c>
       <c r="B9" t="n">
         <v>79679</v>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380171</v>
+        <v>380159</v>
       </c>
       <c r="R9" t="n">
-        <v>6856101</v>
+        <v>6856070</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128715329</v>
+        <v>128713614</v>
       </c>
       <c r="B10" t="n">
-        <v>78061</v>
+        <v>79679</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380141</v>
+        <v>380171</v>
       </c>
       <c r="R10" t="n">
-        <v>6856087</v>
+        <v>6856101</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2128,37 +2128,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128712913</v>
+        <v>128713193</v>
       </c>
       <c r="B15" t="n">
-        <v>79708</v>
+        <v>57793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2166,13 +2179,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380064</v>
+        <v>380089</v>
       </c>
       <c r="R15" t="n">
-        <v>6856024</v>
+        <v>6856030</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2201,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,12 +2224,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,50 +2251,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128713193</v>
+        <v>128712913</v>
       </c>
       <c r="B16" t="n">
-        <v>57793</v>
+        <v>79708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2294,13 +2289,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380089</v>
+        <v>380064</v>
       </c>
       <c r="R16" t="n">
-        <v>6856030</v>
+        <v>6856024</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,7 +2324,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2334,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -2128,50 +2128,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128713193</v>
+        <v>128712913</v>
       </c>
       <c r="B15" t="n">
-        <v>57793</v>
+        <v>79708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2179,13 +2166,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380089</v>
+        <v>380064</v>
       </c>
       <c r="R15" t="n">
-        <v>6856030</v>
+        <v>6856024</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,7 +2211,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,37 +2243,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128712913</v>
+        <v>128713193</v>
       </c>
       <c r="B16" t="n">
-        <v>79708</v>
+        <v>57793</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2289,13 +2294,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380064</v>
+        <v>380089</v>
       </c>
       <c r="R16" t="n">
-        <v>6856024</v>
+        <v>6856030</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,12 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>128714050</v>
       </c>
       <c r="B5" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128724116</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128713332</v>
       </c>
       <c r="B7" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B12" t="n">
-        <v>79679</v>
+        <v>78492</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R12" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128712927</v>
+        <v>128713160</v>
       </c>
       <c r="B13" t="n">
-        <v>78492</v>
+        <v>79679</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380057</v>
+        <v>380089</v>
       </c>
       <c r="R13" t="n">
-        <v>6856033</v>
+        <v>6856030</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2128,37 +2128,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128712913</v>
+        <v>128713193</v>
       </c>
       <c r="B15" t="n">
-        <v>79708</v>
+        <v>57793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2166,13 +2179,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380064</v>
+        <v>380089</v>
       </c>
       <c r="R15" t="n">
-        <v>6856024</v>
+        <v>6856030</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2201,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,12 +2224,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,50 +2251,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128713193</v>
+        <v>128712913</v>
       </c>
       <c r="B16" t="n">
-        <v>57793</v>
+        <v>79708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2294,13 +2289,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380089</v>
+        <v>380064</v>
       </c>
       <c r="R16" t="n">
-        <v>6856030</v>
+        <v>6856024</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,7 +2324,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2334,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2695,7 +2695,7 @@
         <v>128715364</v>
       </c>
       <c r="B20" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128714565</v>
       </c>
       <c r="B2" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128713751</v>
       </c>
       <c r="B3" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128715010</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128714050</v>
       </c>
       <c r="B5" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128724116</v>
       </c>
       <c r="B6" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128713332</v>
       </c>
       <c r="B7" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>128715329</v>
       </c>
       <c r="B8" t="n">
-        <v>78061</v>
+        <v>78088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>128713452</v>
       </c>
       <c r="B9" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128713614</v>
       </c>
       <c r="B10" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>128713378</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128712927</v>
+        <v>128713160</v>
       </c>
       <c r="B12" t="n">
-        <v>78492</v>
+        <v>79706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380057</v>
+        <v>380089</v>
       </c>
       <c r="R12" t="n">
-        <v>6856033</v>
+        <v>6856030</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B13" t="n">
-        <v>79679</v>
+        <v>78519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R13" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2012,7 @@
         <v>128713650</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,50 +2128,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128713193</v>
+        <v>128712913</v>
       </c>
       <c r="B15" t="n">
-        <v>57793</v>
+        <v>79735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2179,13 +2166,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380089</v>
+        <v>380064</v>
       </c>
       <c r="R15" t="n">
-        <v>6856030</v>
+        <v>6856024</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,7 +2211,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,37 +2243,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128712913</v>
+        <v>128713193</v>
       </c>
       <c r="B16" t="n">
-        <v>79708</v>
+        <v>57820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2289,13 +2294,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380064</v>
+        <v>380089</v>
       </c>
       <c r="R16" t="n">
-        <v>6856024</v>
+        <v>6856030</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,12 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,7 +2369,7 @@
         <v>128713709</v>
       </c>
       <c r="B17" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128724114</v>
       </c>
       <c r="B18" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128724111</v>
       </c>
       <c r="B19" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128715364</v>
       </c>
       <c r="B20" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -2128,37 +2128,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128712913</v>
+        <v>128713193</v>
       </c>
       <c r="B15" t="n">
-        <v>79735</v>
+        <v>57820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2166,13 +2179,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380064</v>
+        <v>380089</v>
       </c>
       <c r="R15" t="n">
-        <v>6856024</v>
+        <v>6856030</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2201,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,12 +2224,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,50 +2251,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128713193</v>
+        <v>128712913</v>
       </c>
       <c r="B16" t="n">
-        <v>57820</v>
+        <v>79735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2294,13 +2289,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380089</v>
+        <v>380064</v>
       </c>
       <c r="R16" t="n">
-        <v>6856030</v>
+        <v>6856024</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,7 +2324,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2334,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128714565</v>
+        <v>128713751</v>
       </c>
       <c r="B2" t="n">
-        <v>79735</v>
+        <v>79710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380004</v>
+        <v>380101</v>
       </c>
       <c r="R2" t="n">
-        <v>6856113</v>
+        <v>6856112</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128713751</v>
+        <v>128715010</v>
       </c>
       <c r="B3" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,17 +819,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Larstjärnen, Dlr</t>
+          <t>Smörtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380101</v>
+        <v>380156</v>
       </c>
       <c r="R3" t="n">
-        <v>6856112</v>
+        <v>6855940</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128715010</v>
+        <v>128714565</v>
       </c>
       <c r="B4" t="n">
-        <v>79706</v>
+        <v>79739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Smörtjärnåsen, Dlr</t>
+          <t>Larstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380156</v>
+        <v>380004</v>
       </c>
       <c r="R4" t="n">
-        <v>6855940</v>
+        <v>6856113</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +1008,7 @@
         <v>128714050</v>
       </c>
       <c r="B5" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128724116</v>
       </c>
       <c r="B6" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128713332</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>128715329</v>
       </c>
       <c r="B8" t="n">
-        <v>78088</v>
+        <v>78092</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>128713452</v>
       </c>
       <c r="B9" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128713614</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>128713160</v>
       </c>
       <c r="B12" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128712927</v>
       </c>
       <c r="B13" t="n">
-        <v>78519</v>
+        <v>78523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>128713650</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,50 +2128,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128713193</v>
+        <v>128712913</v>
       </c>
       <c r="B15" t="n">
-        <v>57820</v>
+        <v>79739</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2179,13 +2166,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380089</v>
+        <v>380064</v>
       </c>
       <c r="R15" t="n">
-        <v>6856030</v>
+        <v>6856024</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,7 +2211,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,37 +2243,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128712913</v>
+        <v>128713193</v>
       </c>
       <c r="B16" t="n">
-        <v>79735</v>
+        <v>57820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2289,13 +2294,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380064</v>
+        <v>380089</v>
       </c>
       <c r="R16" t="n">
-        <v>6856024</v>
+        <v>6856030</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,12 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,7 +2369,7 @@
         <v>128713709</v>
       </c>
       <c r="B17" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128724114</v>
       </c>
       <c r="B18" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128724111</v>
       </c>
       <c r="B19" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128715364</v>
       </c>
       <c r="B20" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>128714050</v>
       </c>
       <c r="B5" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128724116</v>
       </c>
       <c r="B6" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128713332</v>
       </c>
       <c r="B7" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2128,37 +2128,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128712913</v>
+        <v>128713193</v>
       </c>
       <c r="B15" t="n">
-        <v>79739</v>
+        <v>57820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2166,13 +2179,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380064</v>
+        <v>380089</v>
       </c>
       <c r="R15" t="n">
-        <v>6856024</v>
+        <v>6856030</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2201,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,12 +2224,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,50 +2251,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128713193</v>
+        <v>128712913</v>
       </c>
       <c r="B16" t="n">
-        <v>57820</v>
+        <v>79739</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2294,13 +2289,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380089</v>
+        <v>380064</v>
       </c>
       <c r="R16" t="n">
-        <v>6856030</v>
+        <v>6856024</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,7 +2324,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2334,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2695,7 +2695,7 @@
         <v>128715364</v>
       </c>
       <c r="B20" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128713751</v>
+        <v>128714565</v>
       </c>
       <c r="B2" t="n">
-        <v>79710</v>
+        <v>79739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380101</v>
+        <v>380004</v>
       </c>
       <c r="R2" t="n">
-        <v>6856112</v>
+        <v>6856113</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128715010</v>
+        <v>128713751</v>
       </c>
       <c r="B3" t="n">
         <v>79710</v>
@@ -819,17 +819,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Smörtjärnåsen, Dlr</t>
+          <t>Larstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380156</v>
+        <v>380101</v>
       </c>
       <c r="R3" t="n">
-        <v>6855940</v>
+        <v>6856112</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128714565</v>
+        <v>128715010</v>
       </c>
       <c r="B4" t="n">
-        <v>79739</v>
+        <v>79710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Larstjärnen, Dlr</t>
+          <t>Smörtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380004</v>
+        <v>380156</v>
       </c>
       <c r="R4" t="n">
-        <v>6856113</v>
+        <v>6855940</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2128,50 +2128,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128713193</v>
+        <v>128712913</v>
       </c>
       <c r="B15" t="n">
-        <v>57820</v>
+        <v>79739</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2179,13 +2166,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380089</v>
+        <v>380064</v>
       </c>
       <c r="R15" t="n">
-        <v>6856030</v>
+        <v>6856024</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,7 +2211,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,37 +2243,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128712913</v>
+        <v>128713193</v>
       </c>
       <c r="B16" t="n">
-        <v>79739</v>
+        <v>57820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2289,13 +2294,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380064</v>
+        <v>380089</v>
       </c>
       <c r="R16" t="n">
-        <v>6856024</v>
+        <v>6856030</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,12 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B12" t="n">
-        <v>79710</v>
+        <v>78523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R12" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128712927</v>
+        <v>128713160</v>
       </c>
       <c r="B13" t="n">
-        <v>78523</v>
+        <v>79710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380057</v>
+        <v>380089</v>
       </c>
       <c r="R13" t="n">
-        <v>6856033</v>
+        <v>6856030</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2366,7 +2366,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128713709</v>
+        <v>128724114</v>
       </c>
       <c r="B17" t="n">
         <v>78878</v>
@@ -2395,22 +2395,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Larstjärnen, Dlr</t>
+          <t>Smörtjärnsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380115</v>
+        <v>380096</v>
       </c>
       <c r="R17" t="n">
-        <v>6856115</v>
+        <v>6855925</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2434,22 +2431,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,25 +2455,26 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128724114</v>
+        <v>128713709</v>
       </c>
       <c r="B18" t="n">
         <v>78878</v>
@@ -2505,19 +2503,22 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Smörtjärnsåsen, Dlr</t>
+          <t>Larstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380096</v>
+        <v>380115</v>
       </c>
       <c r="R18" t="n">
-        <v>6855925</v>
+        <v>6856115</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2541,22 +2542,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,19 +2566,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128714565</v>
       </c>
       <c r="B2" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128713751</v>
       </c>
       <c r="B3" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128715010</v>
       </c>
       <c r="B4" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128714050</v>
       </c>
       <c r="B5" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128724116</v>
       </c>
       <c r="B6" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128713332</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>128715329</v>
       </c>
       <c r="B8" t="n">
-        <v>78092</v>
+        <v>78096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>128713452</v>
       </c>
       <c r="B9" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128713614</v>
       </c>
       <c r="B10" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>128713378</v>
       </c>
       <c r="B11" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128712927</v>
+        <v>128713160</v>
       </c>
       <c r="B12" t="n">
-        <v>78523</v>
+        <v>79714</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380057</v>
+        <v>380089</v>
       </c>
       <c r="R12" t="n">
-        <v>6856033</v>
+        <v>6856030</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B13" t="n">
-        <v>79710</v>
+        <v>78527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R13" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2012,7 @@
         <v>128713650</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128712913</v>
       </c>
       <c r="B15" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>128713193</v>
       </c>
       <c r="B16" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2366,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128724114</v>
+        <v>128713709</v>
       </c>
       <c r="B17" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,19 +2395,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Smörtjärnsåsen, Dlr</t>
+          <t>Larstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380096</v>
+        <v>380115</v>
       </c>
       <c r="R17" t="n">
-        <v>6855925</v>
+        <v>6856115</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2431,22 +2434,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,29 +2458,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128713709</v>
+        <v>128724114</v>
       </c>
       <c r="B18" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,22 +2505,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Larstjärnen, Dlr</t>
+          <t>Smörtjärnsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380115</v>
+        <v>380096</v>
       </c>
       <c r="R18" t="n">
-        <v>6856115</v>
+        <v>6855925</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,22 +2541,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,18 +2565,19 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
         <v>128724111</v>
       </c>
       <c r="B19" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128715364</v>
       </c>
       <c r="B20" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B12" t="n">
-        <v>79714</v>
+        <v>78527</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R12" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128712927</v>
+        <v>128713160</v>
       </c>
       <c r="B13" t="n">
-        <v>78527</v>
+        <v>79714</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380057</v>
+        <v>380089</v>
       </c>
       <c r="R13" t="n">
-        <v>6856033</v>
+        <v>6856030</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128712927</v>
+        <v>128713160</v>
       </c>
       <c r="B12" t="n">
-        <v>78527</v>
+        <v>79714</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380057</v>
+        <v>380089</v>
       </c>
       <c r="R12" t="n">
-        <v>6856033</v>
+        <v>6856030</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B13" t="n">
-        <v>79714</v>
+        <v>78527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R13" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128714565</v>
       </c>
       <c r="B2" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128713751</v>
       </c>
       <c r="B3" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128715010</v>
       </c>
       <c r="B4" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128714050</v>
       </c>
       <c r="B5" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128724116</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128713332</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>128715329</v>
       </c>
       <c r="B8" t="n">
-        <v>78096</v>
+        <v>78037</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>128713452</v>
       </c>
       <c r="B9" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128713614</v>
       </c>
       <c r="B10" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>128713378</v>
       </c>
       <c r="B11" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B12" t="n">
-        <v>79714</v>
+        <v>78432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R12" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128712927</v>
+        <v>128713160</v>
       </c>
       <c r="B13" t="n">
-        <v>78527</v>
+        <v>79619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380057</v>
+        <v>380089</v>
       </c>
       <c r="R13" t="n">
-        <v>6856033</v>
+        <v>6856030</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2012,7 @@
         <v>128713650</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128712913</v>
       </c>
       <c r="B15" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>128713193</v>
       </c>
       <c r="B16" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>128713709</v>
       </c>
       <c r="B17" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128724114</v>
       </c>
       <c r="B18" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128724111</v>
       </c>
       <c r="B19" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128715364</v>
       </c>
       <c r="B20" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128715329</v>
+        <v>128713452</v>
       </c>
       <c r="B8" t="n">
-        <v>78042</v>
+        <v>79624</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380141</v>
+        <v>380159</v>
       </c>
       <c r="R8" t="n">
-        <v>6856087</v>
+        <v>6856070</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,7 +1450,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128713452</v>
+        <v>128713614</v>
       </c>
       <c r="B9" t="n">
         <v>79624</v>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380159</v>
+        <v>380171</v>
       </c>
       <c r="R9" t="n">
-        <v>6856070</v>
+        <v>6856101</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128713614</v>
+        <v>128715329</v>
       </c>
       <c r="B10" t="n">
-        <v>79624</v>
+        <v>78042</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380171</v>
+        <v>380141</v>
       </c>
       <c r="R10" t="n">
-        <v>6856101</v>
+        <v>6856087</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -1008,7 +1008,7 @@
         <v>128714050</v>
       </c>
       <c r="B5" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128724116</v>
       </c>
       <c r="B6" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128713332</v>
       </c>
       <c r="B7" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128713452</v>
+        <v>128715329</v>
       </c>
       <c r="B8" t="n">
-        <v>79624</v>
+        <v>78042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380159</v>
+        <v>380141</v>
       </c>
       <c r="R8" t="n">
-        <v>6856070</v>
+        <v>6856087</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128715329</v>
+        <v>128713452</v>
       </c>
       <c r="B10" t="n">
-        <v>78042</v>
+        <v>79624</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380141</v>
+        <v>380159</v>
       </c>
       <c r="R10" t="n">
-        <v>6856087</v>
+        <v>6856070</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2366,7 +2366,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128713709</v>
+        <v>128724114</v>
       </c>
       <c r="B17" t="n">
         <v>78792</v>
@@ -2395,22 +2395,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Larstjärnen, Dlr</t>
+          <t>Smörtjärnsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380115</v>
+        <v>380096</v>
       </c>
       <c r="R17" t="n">
-        <v>6856115</v>
+        <v>6855925</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2434,22 +2431,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,25 +2455,26 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128724114</v>
+        <v>128713709</v>
       </c>
       <c r="B18" t="n">
         <v>78792</v>
@@ -2505,19 +2503,22 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Smörtjärnsåsen, Dlr</t>
+          <t>Larstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380096</v>
+        <v>380115</v>
       </c>
       <c r="R18" t="n">
-        <v>6855925</v>
+        <v>6856115</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2541,22 +2542,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,19 +2566,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2695,7 +2695,7 @@
         <v>128715364</v>
       </c>
       <c r="B20" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128714565</v>
       </c>
       <c r="B2" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128713751</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128715010</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128714050</v>
       </c>
       <c r="B5" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128724116</v>
       </c>
       <c r="B6" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128713332</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128715329</v>
+        <v>128713452</v>
       </c>
       <c r="B8" t="n">
-        <v>78042</v>
+        <v>79625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380141</v>
+        <v>380159</v>
       </c>
       <c r="R8" t="n">
-        <v>6856087</v>
+        <v>6856070</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,7 +1453,7 @@
         <v>128713614</v>
       </c>
       <c r="B9" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128713452</v>
+        <v>128715329</v>
       </c>
       <c r="B10" t="n">
-        <v>79624</v>
+        <v>78043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380159</v>
+        <v>380141</v>
       </c>
       <c r="R10" t="n">
-        <v>6856070</v>
+        <v>6856087</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128712927</v>
+        <v>128713160</v>
       </c>
       <c r="B12" t="n">
-        <v>78437</v>
+        <v>79625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380057</v>
+        <v>380089</v>
       </c>
       <c r="R12" t="n">
-        <v>6856033</v>
+        <v>6856030</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B13" t="n">
-        <v>79624</v>
+        <v>78438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R13" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2012,7 @@
         <v>128713650</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,37 +2128,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128712913</v>
+        <v>128713193</v>
       </c>
       <c r="B15" t="n">
-        <v>79653</v>
+        <v>57827</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2166,13 +2179,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380064</v>
+        <v>380089</v>
       </c>
       <c r="R15" t="n">
-        <v>6856024</v>
+        <v>6856030</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2201,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,12 +2224,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,50 +2251,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128713193</v>
+        <v>128712913</v>
       </c>
       <c r="B16" t="n">
-        <v>57827</v>
+        <v>79654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2294,13 +2289,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380089</v>
+        <v>380064</v>
       </c>
       <c r="R16" t="n">
-        <v>6856030</v>
+        <v>6856024</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,7 +2324,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2334,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,10 +2366,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128724114</v>
+        <v>128713709</v>
       </c>
       <c r="B17" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,19 +2395,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Smörtjärnsåsen, Dlr</t>
+          <t>Larstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380096</v>
+        <v>380115</v>
       </c>
       <c r="R17" t="n">
-        <v>6855925</v>
+        <v>6856115</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2431,22 +2434,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,29 +2458,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128713709</v>
+        <v>128724114</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,22 +2505,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Larstjärnen, Dlr</t>
+          <t>Smörtjärnsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380115</v>
+        <v>380096</v>
       </c>
       <c r="R18" t="n">
-        <v>6856115</v>
+        <v>6855925</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,22 +2541,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,18 +2565,19 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2587,7 +2587,7 @@
         <v>128724111</v>
       </c>
       <c r="B19" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128715364</v>
       </c>
       <c r="B20" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128714565</v>
+        <v>128713751</v>
       </c>
       <c r="B2" t="n">
-        <v>79654</v>
+        <v>79625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380004</v>
+        <v>380101</v>
       </c>
       <c r="R2" t="n">
-        <v>6856113</v>
+        <v>6856112</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128713751</v>
+        <v>128715010</v>
       </c>
       <c r="B3" t="n">
         <v>79625</v>
@@ -819,17 +819,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Larstjärnen, Dlr</t>
+          <t>Smörtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380101</v>
+        <v>380156</v>
       </c>
       <c r="R3" t="n">
-        <v>6856112</v>
+        <v>6855940</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128715010</v>
+        <v>128714565</v>
       </c>
       <c r="B4" t="n">
-        <v>79625</v>
+        <v>79654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Smörtjärnåsen, Dlr</t>
+          <t>Larstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380156</v>
+        <v>380004</v>
       </c>
       <c r="R4" t="n">
-        <v>6855940</v>
+        <v>6856113</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128713452</v>
+        <v>128715329</v>
       </c>
       <c r="B8" t="n">
-        <v>79625</v>
+        <v>78043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380159</v>
+        <v>380141</v>
       </c>
       <c r="R8" t="n">
-        <v>6856070</v>
+        <v>6856087</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,7 +1450,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128713614</v>
+        <v>128713452</v>
       </c>
       <c r="B9" t="n">
         <v>79625</v>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380171</v>
+        <v>380159</v>
       </c>
       <c r="R9" t="n">
-        <v>6856101</v>
+        <v>6856070</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128715329</v>
+        <v>128713614</v>
       </c>
       <c r="B10" t="n">
-        <v>78043</v>
+        <v>79625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380141</v>
+        <v>380171</v>
       </c>
       <c r="R10" t="n">
-        <v>6856087</v>
+        <v>6856101</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2128,50 +2128,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128713193</v>
+        <v>128712913</v>
       </c>
       <c r="B15" t="n">
-        <v>57827</v>
+        <v>79654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2179,13 +2166,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380089</v>
+        <v>380064</v>
       </c>
       <c r="R15" t="n">
-        <v>6856030</v>
+        <v>6856024</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,7 +2211,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,37 +2243,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128712913</v>
+        <v>128713193</v>
       </c>
       <c r="B16" t="n">
-        <v>79654</v>
+        <v>57827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2289,13 +2294,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380064</v>
+        <v>380089</v>
       </c>
       <c r="R16" t="n">
-        <v>6856024</v>
+        <v>6856030</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,12 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128713751</v>
+        <v>128714565</v>
       </c>
       <c r="B2" t="n">
-        <v>79625</v>
+        <v>79654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380101</v>
+        <v>380004</v>
       </c>
       <c r="R2" t="n">
-        <v>6856112</v>
+        <v>6856113</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128715010</v>
+        <v>128713751</v>
       </c>
       <c r="B3" t="n">
         <v>79625</v>
@@ -819,17 +819,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Smörtjärnåsen, Dlr</t>
+          <t>Larstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380156</v>
+        <v>380101</v>
       </c>
       <c r="R3" t="n">
-        <v>6855940</v>
+        <v>6856112</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128714565</v>
+        <v>128715010</v>
       </c>
       <c r="B4" t="n">
-        <v>79654</v>
+        <v>79625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,14 +929,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Larstjärnen, Dlr</t>
+          <t>Smörtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380004</v>
+        <v>380156</v>
       </c>
       <c r="R4" t="n">
-        <v>6856113</v>
+        <v>6855940</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B12" t="n">
-        <v>79625</v>
+        <v>78438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R12" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128712927</v>
+        <v>128713160</v>
       </c>
       <c r="B13" t="n">
-        <v>78438</v>
+        <v>79625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380057</v>
+        <v>380089</v>
       </c>
       <c r="R13" t="n">
-        <v>6856033</v>
+        <v>6856030</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128715329</v>
+        <v>128713452</v>
       </c>
       <c r="B8" t="n">
-        <v>78043</v>
+        <v>79625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380141</v>
+        <v>380159</v>
       </c>
       <c r="R8" t="n">
-        <v>6856087</v>
+        <v>6856070</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,7 +1450,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128713452</v>
+        <v>128713614</v>
       </c>
       <c r="B9" t="n">
         <v>79625</v>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380159</v>
+        <v>380171</v>
       </c>
       <c r="R9" t="n">
-        <v>6856070</v>
+        <v>6856101</v>
       </c>
       <c r="S9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128713614</v>
+        <v>128715329</v>
       </c>
       <c r="B10" t="n">
-        <v>79625</v>
+        <v>78043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380171</v>
+        <v>380141</v>
       </c>
       <c r="R10" t="n">
-        <v>6856101</v>
+        <v>6856087</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2128,37 +2128,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128712913</v>
+        <v>128713193</v>
       </c>
       <c r="B15" t="n">
-        <v>79654</v>
+        <v>57827</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2166,13 +2179,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380064</v>
+        <v>380089</v>
       </c>
       <c r="R15" t="n">
-        <v>6856024</v>
+        <v>6856030</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2201,7 +2214,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,12 +2224,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,50 +2251,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128713193</v>
+        <v>128712913</v>
       </c>
       <c r="B16" t="n">
-        <v>57827</v>
+        <v>79654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2294,13 +2289,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380089</v>
+        <v>380064</v>
       </c>
       <c r="R16" t="n">
-        <v>6856030</v>
+        <v>6856024</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,7 +2324,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2334,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128714565</v>
       </c>
       <c r="B2" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128713751</v>
       </c>
       <c r="B3" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128715010</v>
       </c>
       <c r="B4" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128714050</v>
       </c>
       <c r="B5" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128724116</v>
       </c>
       <c r="B6" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128713332</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>128713452</v>
       </c>
       <c r="B8" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>128713614</v>
       </c>
       <c r="B9" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128715329</v>
       </c>
       <c r="B10" t="n">
-        <v>78043</v>
+        <v>78047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>128713378</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128712927</v>
+        <v>128713160</v>
       </c>
       <c r="B12" t="n">
-        <v>78438</v>
+        <v>79629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380057</v>
+        <v>380089</v>
       </c>
       <c r="R12" t="n">
-        <v>6856033</v>
+        <v>6856030</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B13" t="n">
-        <v>79625</v>
+        <v>78442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R13" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2012,7 @@
         <v>128713650</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,50 +2128,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128713193</v>
+        <v>128712913</v>
       </c>
       <c r="B15" t="n">
-        <v>57827</v>
+        <v>79658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2179,13 +2166,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380089</v>
+        <v>380064</v>
       </c>
       <c r="R15" t="n">
-        <v>6856030</v>
+        <v>6856024</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,7 +2211,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer på stående död tallved</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,37 +2243,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128712913</v>
+        <v>128713193</v>
       </c>
       <c r="B16" t="n">
-        <v>79654</v>
+        <v>57829</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2289,13 +2294,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380064</v>
+        <v>380089</v>
       </c>
       <c r="R16" t="n">
-        <v>6856024</v>
+        <v>6856030</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2334,12 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Växer på stående död tallved</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,7 +2369,7 @@
         <v>128713709</v>
       </c>
       <c r="B17" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128724114</v>
       </c>
       <c r="B18" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128724111</v>
       </c>
       <c r="B19" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128715364</v>
       </c>
       <c r="B20" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128713452</v>
+        <v>128715329</v>
       </c>
       <c r="B8" t="n">
-        <v>79629</v>
+        <v>78047</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380159</v>
+        <v>380141</v>
       </c>
       <c r="R8" t="n">
-        <v>6856070</v>
+        <v>6856087</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,7 +1450,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128713614</v>
+        <v>128713452</v>
       </c>
       <c r="B9" t="n">
         <v>79629</v>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380171</v>
+        <v>380159</v>
       </c>
       <c r="R9" t="n">
-        <v>6856101</v>
+        <v>6856070</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128715329</v>
+        <v>128713614</v>
       </c>
       <c r="B10" t="n">
-        <v>78047</v>
+        <v>79629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,21 +1571,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380141</v>
+        <v>380171</v>
       </c>
       <c r="R10" t="n">
-        <v>6856087</v>
+        <v>6856101</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B12" t="n">
-        <v>79629</v>
+        <v>78442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R12" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128712927</v>
+        <v>128713160</v>
       </c>
       <c r="B13" t="n">
-        <v>78442</v>
+        <v>79629</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380057</v>
+        <v>380089</v>
       </c>
       <c r="R13" t="n">
-        <v>6856033</v>
+        <v>6856030</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -1789,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128712927</v>
+        <v>128713160</v>
       </c>
       <c r="B12" t="n">
-        <v>78442</v>
+        <v>79629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,21 +1800,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,13 +1827,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380057</v>
+        <v>380089</v>
       </c>
       <c r="R12" t="n">
-        <v>6856033</v>
+        <v>6856030</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128713160</v>
+        <v>128712927</v>
       </c>
       <c r="B13" t="n">
-        <v>79629</v>
+        <v>78442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380089</v>
+        <v>380057</v>
       </c>
       <c r="R13" t="n">
-        <v>6856030</v>
+        <v>6856033</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128714565</v>
       </c>
       <c r="B2" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128713751</v>
       </c>
       <c r="B3" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128715010</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128714050</v>
       </c>
       <c r="B5" t="n">
-        <v>92826</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>128724116</v>
       </c>
       <c r="B6" t="n">
-        <v>92826</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>128713332</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>128715329</v>
       </c>
       <c r="B8" t="n">
-        <v>78047</v>
+        <v>78049</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>128713452</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>128713614</v>
       </c>
       <c r="B10" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>128713378</v>
       </c>
       <c r="B11" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>128713160</v>
       </c>
       <c r="B12" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128712927</v>
       </c>
       <c r="B13" t="n">
-        <v>78442</v>
+        <v>78444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>128713650</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>128712913</v>
       </c>
       <c r="B15" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>128713193</v>
       </c>
       <c r="B16" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>128713709</v>
       </c>
       <c r="B17" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128724114</v>
       </c>
       <c r="B18" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>128724111</v>
       </c>
       <c r="B19" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128715364</v>
       </c>
       <c r="B20" t="n">
-        <v>91497</v>
+        <v>91506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40444-2025 artfynd.xlsx
+++ b/artfynd/A 40444-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128713332</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128714050</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128724116</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128715364</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128713650</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128712927</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1465,6 +1500,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128712913</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1575,6 +1615,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128714565</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128715329</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1804,6 +1854,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128713378</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1927,6 +1982,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128713193</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2037,6 +2097,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128713709</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2145,6 +2210,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128724114</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2255,6 +2325,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128713160</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2365,6 +2440,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128713452</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2475,6 +2555,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128713614</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2585,6 +2670,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128713751</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2695,6 +2785,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128715010</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2803,8 +2898,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128724111</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>